--- a/artfynd/A 29375-2022 artfynd.xlsx
+++ b/artfynd/A 29375-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 29375-2022 artfynd.xlsx
+++ b/artfynd/A 29375-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>2832204</v>
       </c>
       <c r="B2" t="n">
-        <v>96309</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99093</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -729,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>349742.7241057861</v>
+        <v>349743</v>
       </c>
       <c r="R2" t="n">
-        <v>6472836.540205671</v>
+        <v>6472837</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -762,19 +757,9 @@
           <t>2001-07-24</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2001-07-24</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -803,6 +788,120 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>16090522</v>
+      </c>
+      <c r="B3" t="n">
+        <v>99093</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>219797</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Purpurknipprot</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Epipactis atrorubens</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Besser</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Halleberg, Uggledalen SO, Vg</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>349746</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6472830</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Vänersborg</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Västra Tunhem</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2014-07-09</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2014-07-09</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Återfunnen efter 13 år. Då hittades 4 stänglar, nu 11.</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Vägkant i barrskog</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Anita Stridvall</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Anita Stridvall</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
